--- a/Data/FA/FA_Quizzes.xlsx
+++ b/Data/FA/FA_Quizzes.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PyCode\mba\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PyCode\mba\Data\FA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CB26E1A-47CD-49E7-91EC-1C44539305FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDDFA630-BEDE-4BE0-BA1E-69D9BAA9286F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{7CC42CD0-27C3-4497-AFAD-771A8D36D3B3}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1605" uniqueCount="979">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="978">
   <si>
     <t>Sales</t>
   </si>
@@ -85,9 +85,6 @@
     <t xml:space="preserve">Question 8 </t>
   </si>
   <si>
-    <t>That’s in Revisit the module for this week.</t>
-  </si>
-  <si>
     <t>Book Value</t>
   </si>
   <si>
@@ -403,9 +400,6 @@
     <t xml:space="preserve">Question 1 </t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
     <t>Option_D</t>
   </si>
   <si>
@@ -670,9 +664,6 @@
     <t>Real accounts considers two aspect of assets</t>
   </si>
   <si>
-    <t>That’s correct</t>
-  </si>
-  <si>
     <t>Ledger entry</t>
   </si>
   <si>
@@ -700,9 +691,6 @@
     <t>Credit transactions that are recorded in various types of Journals.</t>
   </si>
   <si>
-    <t xml:space="preserve">That's </t>
-  </si>
-  <si>
     <t>Debit</t>
   </si>
   <si>
@@ -733,9 +721,6 @@
     <t>To identify the purpose for which the transactions are posted are called:</t>
   </si>
   <si>
-    <t>That's correct</t>
-  </si>
-  <si>
     <t>Balance sheet</t>
   </si>
   <si>
@@ -1885,9 +1870,6 @@
     <t>Goodwill cannot be seen, felt, transported physically, it is very real is called:</t>
   </si>
   <si>
-    <t> </t>
-  </si>
-  <si>
     <t>When the company has losses</t>
   </si>
   <si>
@@ -2984,6 +2966,21 @@
   </si>
   <si>
     <t>Misstatements resulting from misappropriation of assets</t>
+  </si>
+  <si>
+    <t>Answer</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
   </si>
 </sst>
 </file>
@@ -3107,7 +3104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -3121,6 +3118,9 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3470,178 +3470,186 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>118</v>
+        <v>973</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="G2" s="4"/>
+        <v>111</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="G3" s="7"/>
+        <v>48</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" s="7"/>
+        <v>36</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>12</v>
+        <v>974</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>12</v>
+        <v>974</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>12</v>
+        <v>976</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -3663,7 +3671,9 @@
       <c r="F9" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G9" s="4"/>
+      <c r="G9" s="4" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
@@ -3684,242 +3694,262 @@
       <c r="F10" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="G10" s="1"/>
+      <c r="G10" s="1" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="G11" s="7"/>
+        <v>105</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="G12" s="4"/>
+        <v>99</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>12</v>
+        <v>975</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="G14" s="4"/>
+        <v>87</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="G15" s="7"/>
+        <v>81</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D16" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F16" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="E16" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="G16" s="4"/>
+      <c r="G16" s="4" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="G17" s="7"/>
+        <v>72</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="G18" s="4"/>
+        <v>66</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="G19" s="7"/>
+        <v>60</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>12</v>
+        <v>977</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G21" s="4"/>
+        <v>42</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>975</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3943,456 +3973,486 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>118</v>
+        <v>973</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>804</v>
+        <v>798</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>803</v>
+        <v>797</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>802</v>
+        <v>796</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>801</v>
+        <v>795</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>800</v>
-      </c>
-      <c r="G2" s="4"/>
+        <v>794</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>760</v>
-      </c>
-      <c r="G3" s="7"/>
+        <v>754</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>754</v>
+        <v>748</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="G4" s="7"/>
+        <v>742</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>753</v>
+        <v>747</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>750</v>
-      </c>
-      <c r="G5" s="4"/>
+        <v>744</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>749</v>
+        <v>743</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>745</v>
-      </c>
-      <c r="G6" s="7"/>
+        <v>739</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>740</v>
-      </c>
-      <c r="G7" s="4"/>
+        <v>734</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>735</v>
-      </c>
-      <c r="G8" s="7"/>
+        <v>729</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>730</v>
-      </c>
-      <c r="G9" s="4"/>
+        <v>724</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>12</v>
+        <v>977</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>799</v>
+        <v>793</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>798</v>
+        <v>792</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>796</v>
+        <v>790</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>795</v>
+        <v>789</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>12</v>
+        <v>974</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>794</v>
+        <v>788</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>793</v>
+        <v>787</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>792</v>
+        <v>786</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>791</v>
+        <v>785</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>12</v>
+        <v>976</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>790</v>
+        <v>784</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>789</v>
+        <v>783</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>788</v>
+        <v>782</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>757</v>
+        <v>751</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>12</v>
+        <v>977</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>787</v>
+        <v>781</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>786</v>
+        <v>780</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>785</v>
+        <v>779</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>784</v>
-      </c>
-      <c r="G14" s="4"/>
+        <v>778</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>783</v>
+        <v>777</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>782</v>
+        <v>776</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>12</v>
+        <v>974</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>774</v>
+        <v>768</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>775</v>
+        <v>769</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>773</v>
+        <v>767</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>776</v>
-      </c>
-      <c r="G16" s="4"/>
+        <v>770</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>778</v>
+        <v>772</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>756</v>
+        <v>750</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>757</v>
+        <v>751</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>758</v>
-      </c>
-      <c r="G17" s="7"/>
+        <v>752</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>776</v>
+        <v>770</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>775</v>
+        <v>769</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>774</v>
+        <v>768</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>773</v>
-      </c>
-      <c r="G18" s="4"/>
+        <v>767</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>772</v>
+        <v>766</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>757</v>
+        <v>751</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>756</v>
+        <v>750</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>770</v>
-      </c>
-      <c r="G19" s="7"/>
+        <v>764</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>768</v>
+        <v>762</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>765</v>
-      </c>
-      <c r="G20" s="4"/>
+        <v>759</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>758</v>
+        <v>752</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>757</v>
+        <v>751</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>756</v>
+        <v>750</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>755</v>
-      </c>
-      <c r="G21" s="4"/>
+        <v>749</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>976</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4415,452 +4475,486 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>118</v>
+        <v>973</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>891</v>
+        <v>885</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>890</v>
+        <v>884</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>889</v>
+        <v>883</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>888</v>
-      </c>
-      <c r="G2" s="4"/>
+        <v>882</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>841</v>
+        <v>835</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>840</v>
+        <v>834</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>839</v>
+        <v>833</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>838</v>
+        <v>832</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>837</v>
-      </c>
-      <c r="G3" s="7"/>
+        <v>831</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>833</v>
+        <v>827</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>832</v>
+        <v>826</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>831</v>
+        <v>825</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>830</v>
+        <v>824</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>829</v>
-      </c>
-      <c r="G4" s="7"/>
+        <v>823</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>828</v>
+        <v>822</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>827</v>
+        <v>821</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>826</v>
+        <v>820</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>825</v>
+        <v>819</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>824</v>
+        <v>818</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>12</v>
+        <v>975</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>12</v>
+        <v>976</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>819</v>
+        <v>813</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>809</v>
-      </c>
-      <c r="G7" s="4"/>
+        <v>803</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>815</v>
+        <v>809</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>814</v>
+        <v>808</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>813</v>
-      </c>
-      <c r="G8" s="7"/>
+        <v>807</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>808</v>
-      </c>
-      <c r="G9" s="4"/>
+        <v>802</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>806</v>
+        <v>800</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>805</v>
+        <v>799</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="G10" s="1"/>
+        <v>279</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>887</v>
+        <v>881</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>886</v>
+        <v>880</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>885</v>
+        <v>879</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>884</v>
+        <v>878</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>883</v>
-      </c>
-      <c r="G11" s="7"/>
+        <v>877</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>882</v>
+        <v>876</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>881</v>
+        <v>875</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>880</v>
+        <v>874</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>879</v>
+        <v>873</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>806</v>
-      </c>
-      <c r="G12" s="4"/>
+        <v>800</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>877</v>
+        <v>871</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>876</v>
+        <v>870</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>875</v>
+        <v>869</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>874</v>
-      </c>
-      <c r="G13" s="7"/>
+        <v>868</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>873</v>
+        <v>867</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>872</v>
+        <v>866</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>871</v>
+        <v>865</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>870</v>
+        <v>864</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>869</v>
-      </c>
-      <c r="G14" s="4"/>
+        <v>863</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>867</v>
+        <v>861</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>866</v>
+        <v>860</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>865</v>
+        <v>859</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>217</v>
+        <v>975</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>864</v>
+        <v>858</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>863</v>
+        <v>857</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>862</v>
+        <v>856</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>861</v>
+        <v>855</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>860</v>
-      </c>
-      <c r="G16" s="4"/>
+        <v>854</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>859</v>
+        <v>853</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>858</v>
+        <v>852</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>857</v>
+        <v>851</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>855</v>
-      </c>
-      <c r="G17" s="7"/>
+        <v>849</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>854</v>
+        <v>848</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>853</v>
+        <v>847</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>852</v>
+        <v>846</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>851</v>
+        <v>845</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>850</v>
-      </c>
-      <c r="G18" s="4"/>
+        <v>844</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>849</v>
+        <v>843</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>848</v>
+        <v>842</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>843</v>
+        <v>837</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>847</v>
+        <v>841</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>846</v>
-      </c>
-      <c r="G19" s="7"/>
+        <v>840</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>845</v>
+        <v>839</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>844</v>
+        <v>838</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>843</v>
+        <v>837</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>842</v>
-      </c>
-      <c r="G20" s="4"/>
+        <v>836</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>834</v>
-      </c>
-      <c r="G21" s="4"/>
+        <v>828</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>977</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4870,7 +4964,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2471A702-982B-4513-BEF5-1113DE68CE25}">
   <sheetPr codeName="Sheet13"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -4881,424 +4975,487 @@
     <col min="6" max="6" width="57.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>971</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>970</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>969</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>968</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>927</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>926</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>925</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>924</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>923</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>917</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>916</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>915</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>914</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>913</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>912</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>911</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>910</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>909</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>908</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>907</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>906</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>905</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>904</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>903</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>902</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>901</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>900</v>
+      </c>
+      <c r="G7" s="14" t="s">
         <v>977</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>976</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>975</v>
-      </c>
-      <c r="F2" s="4" t="s">
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>899</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>898</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>897</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>896</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>895</v>
+      </c>
+      <c r="G8" s="15" t="s">
         <v>974</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>933</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>932</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>931</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>930</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>929</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>923</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>922</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>281</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>921</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>919</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>918</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>917</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>916</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>914</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>913</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>912</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>911</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>909</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>908</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>907</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>437</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>905</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>904</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>903</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>902</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>900</v>
+        <v>894</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>899</v>
+        <v>893</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>844</v>
+        <v>838</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>891</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>896</v>
+        <v>890</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>894</v>
+        <v>888</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>893</v>
+        <v>887</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+        <v>886</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>973</v>
+        <v>967</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>972</v>
+        <v>966</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>971</v>
+        <v>965</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>970</v>
+        <v>964</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>969</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+        <v>963</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>968</v>
+        <v>962</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>967</v>
+        <v>961</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>966</v>
+        <v>960</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>965</v>
+        <v>959</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>964</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+        <v>958</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>963</v>
+        <v>957</v>
       </c>
       <c r="C13" s="8" t="s">
+        <v>943</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>946</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>945</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>944</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>956</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>955</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>954</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>953</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>952</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>951</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>938</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>939</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>950</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>941</v>
+      </c>
+      <c r="G15" s="14" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>949</v>
       </c>
-      <c r="D13" s="8" t="s">
-        <v>952</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>951</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>962</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>961</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>960</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>959</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>958</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>957</v>
-      </c>
-      <c r="C15" s="8" t="s">
+      <c r="C16" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>829</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>948</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>947</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>946</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>945</v>
+      </c>
+      <c r="E17" s="8" t="s">
         <v>944</v>
       </c>
-      <c r="D15" s="8" t="s">
-        <v>945</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>956</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>955</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>835</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>954</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>953</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>952</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>951</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>950</v>
-      </c>
       <c r="F17" s="7" t="s">
-        <v>949</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+        <v>943</v>
+      </c>
+      <c r="G17" s="14" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>948</v>
+        <v>942</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>947</v>
+        <v>941</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>946</v>
+        <v>940</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>944</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+        <v>938</v>
+      </c>
+      <c r="G18" s="14" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>943</v>
+        <v>937</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>942</v>
+        <v>936</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>941</v>
+        <v>935</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>940</v>
+        <v>934</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+        <v>933</v>
+      </c>
+      <c r="G19" s="14" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>938</v>
+        <v>932</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>937</v>
+        <v>931</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>935</v>
+        <v>929</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>934</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+        <v>928</v>
+      </c>
+      <c r="G20" s="14" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>928</v>
+        <v>922</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>926</v>
+        <v>920</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>925</v>
+        <v>919</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>924</v>
+        <v>918</v>
+      </c>
+      <c r="G21" s="14" t="s">
+        <v>977</v>
       </c>
     </row>
   </sheetData>
@@ -5323,450 +5480,486 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>118</v>
+        <v>973</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="G2" s="4"/>
+        <v>178</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="G3" s="7"/>
+        <v>163</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="G4" s="7"/>
+        <v>153</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="G5" s="4"/>
+        <v>148</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="G6" s="7"/>
+        <v>143</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="G7" s="4"/>
+        <v>138</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="G8" s="7"/>
+        <v>133</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="G9" s="4"/>
+        <v>128</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G10" s="1"/>
+        <v>123</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>207</v>
+        <v>976</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="G12" s="4"/>
+        <v>200</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="G13" s="7"/>
+        <v>195</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="G14" s="4"/>
+        <v>188</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C15" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="F15" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="D15" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="G15" s="7"/>
+      <c r="G15" s="7" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="G16" s="4"/>
+        <v>185</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="G17" s="7"/>
+        <v>180</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>12</v>
+        <v>976</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>2</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="G19" s="7"/>
+        <v>173</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="G20" s="4"/>
+        <v>168</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="G21" s="4"/>
+        <v>158</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>974</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5790,180 +5983,186 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>118</v>
+        <v>973</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>217</v>
+        <v>976</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="G3" s="7"/>
+        <v>245</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="G4" s="7"/>
+        <v>236</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>217</v>
+        <v>975</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="G6" s="7"/>
+        <v>226</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>228</v>
+        <v>974</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>217</v>
+        <v>976</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -5971,22 +6170,22 @@
         <v>11</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>217</v>
+        <v>975</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -5994,266 +6193,276 @@
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>12</v>
+        <v>975</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>217</v>
+        <v>975</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>217</v>
+        <v>975</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>217</v>
+        <v>976</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="G14" s="4"/>
+        <v>72</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>217</v>
+        <v>974</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>12</v>
+        <v>975</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>217</v>
+        <v>976</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="G18" s="4"/>
+        <v>257</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="G19" s="7"/>
+        <v>254</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="G20" s="4"/>
+        <v>249</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="G21" s="4"/>
+        <v>240</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>974</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6277,450 +6486,486 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>118</v>
+        <v>973</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>217</v>
+        <v>974</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="G3" s="7"/>
+        <v>311</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="G4" s="7"/>
+        <v>211</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="G5" s="4"/>
+        <v>301</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="C6" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="E6" s="8" t="s">
         <v>298</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>304</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>303</v>
-      </c>
       <c r="F6" s="8" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>217</v>
+        <v>976</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="G7" s="4"/>
+        <v>293</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="G8" s="7"/>
+        <v>291</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="G9" s="4"/>
+        <v>287</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="G10" s="1"/>
+        <v>283</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="G11" s="7"/>
+        <v>284</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="G12" s="4"/>
+        <v>347</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>349</v>
-      </c>
-      <c r="G13" s="7"/>
+        <v>344</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="G14" s="4"/>
+        <v>341</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>342</v>
-      </c>
-      <c r="G15" s="7"/>
+        <v>337</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="G16" s="4"/>
+        <v>332</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="G17" s="7"/>
+        <v>328</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="G18" s="4"/>
+        <v>325</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>326</v>
-      </c>
-      <c r="G19" s="7"/>
+        <v>321</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="G20" s="4"/>
+        <v>316</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="G21" s="4"/>
+        <v>306</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>975</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6744,186 +6989,186 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>118</v>
+        <v>973</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>217</v>
+        <v>974</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>217</v>
+        <v>977</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>217</v>
+        <v>975</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>2</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>217</v>
+        <v>976</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>2</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>217</v>
+        <v>974</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>217</v>
+        <v>975</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>217</v>
+        <v>977</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -6931,22 +7176,22 @@
         <v>11</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>217</v>
+        <v>974</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -6954,275 +7199,275 @@
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>217</v>
+        <v>975</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>217</v>
+        <v>975</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>217</v>
+        <v>974</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>217</v>
+        <v>976</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>217</v>
+        <v>974</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>217</v>
+        <v>977</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>217</v>
+        <v>975</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>217</v>
+        <v>975</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>217</v>
+        <v>976</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>217</v>
+        <v>974</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>217</v>
+        <v>975</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>217</v>
+        <v>977</v>
       </c>
     </row>
   </sheetData>
@@ -7247,184 +7492,186 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>118</v>
+        <v>973</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>503</v>
-      </c>
-      <c r="G2" s="4"/>
+        <v>498</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>217</v>
+        <v>977</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>217</v>
+        <v>977</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>217</v>
+        <v>974</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="D6" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>440</v>
+      </c>
+      <c r="F6" s="8" t="s">
         <v>444</v>
       </c>
-      <c r="E6" s="8" t="s">
-        <v>445</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>449</v>
-      </c>
       <c r="G6" s="7" t="s">
-        <v>217</v>
+        <v>976</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>217</v>
+        <v>977</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>228</v>
+        <v>976</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -7432,22 +7679,22 @@
         <v>11</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>217</v>
+        <v>977</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -7455,275 +7702,275 @@
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>217</v>
+        <v>977</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>217</v>
+        <v>976</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>217</v>
+        <v>977</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>12</v>
+        <v>974</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>228</v>
+        <v>974</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>217</v>
+        <v>975</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>217</v>
+        <v>975</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>217</v>
+        <v>974</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="C18" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="D18" s="5" t="s">
         <v>472</v>
       </c>
-      <c r="D18" s="5" t="s">
-        <v>477</v>
-      </c>
       <c r="E18" s="5" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>217</v>
+        <v>976</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>217</v>
+        <v>975</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>12</v>
+        <v>974</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>12</v>
+        <v>975</v>
       </c>
     </row>
   </sheetData>
@@ -7746,458 +7993,486 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>118</v>
+        <v>973</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>217</v>
+        <v>976</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>217</v>
+        <v>976</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>217</v>
+        <v>975</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>526</v>
-      </c>
-      <c r="G5" s="4"/>
+        <v>521</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>521</v>
-      </c>
-      <c r="G6" s="7"/>
+        <v>516</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>515</v>
-      </c>
-      <c r="G7" s="4"/>
+        <v>510</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>516</v>
-      </c>
-      <c r="G8" s="7"/>
+        <v>511</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>513</v>
-      </c>
-      <c r="G9" s="4"/>
+        <v>508</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>12</v>
+        <v>977</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>527</v>
-      </c>
-      <c r="G11" s="7"/>
+        <v>522</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>564</v>
-      </c>
-      <c r="G12" s="4"/>
+        <v>559</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>510</v>
-      </c>
-      <c r="G13" s="7"/>
+        <v>505</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>559</v>
-      </c>
-      <c r="G14" s="4"/>
+        <v>554</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>12</v>
+        <v>977</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>551</v>
-      </c>
-      <c r="G16" s="4"/>
+        <v>546</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>548</v>
-      </c>
-      <c r="G17" s="7"/>
+        <v>543</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>533</v>
-      </c>
-      <c r="G18" s="4"/>
+        <v>528</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>12</v>
+        <v>976</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="G20" s="4"/>
+        <v>527</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>531</v>
-      </c>
-      <c r="G21" s="4"/>
+        <v>526</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>974</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8221,180 +8496,186 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>118</v>
+        <v>973</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>565</v>
-      </c>
-      <c r="G2" s="4"/>
+        <v>560</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>527</v>
-      </c>
-      <c r="G3" s="7"/>
+        <v>522</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>12</v>
+        <v>974</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>12</v>
+        <v>975</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>12</v>
+        <v>974</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>586</v>
-      </c>
-      <c r="G7" s="4"/>
+        <v>581</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>12</v>
+        <v>976</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -8402,277 +8683,299 @@
         <v>11</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>576</v>
-      </c>
-      <c r="G9" s="4"/>
+        <v>571</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="G10" s="1"/>
+        <v>566</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>642</v>
-      </c>
-      <c r="G11" s="7"/>
+        <v>636</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G12" s="4"/>
+      <c r="G12" s="4" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>283</v>
-      </c>
-      <c r="G13" s="7"/>
+        <v>278</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>365</v>
-      </c>
-      <c r="G14" s="4"/>
+        <v>360</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>426</v>
-      </c>
-      <c r="G15" s="7"/>
+        <v>421</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>430</v>
-      </c>
-      <c r="G16" s="4"/>
+        <v>425</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>624</v>
-      </c>
-      <c r="G17" s="7"/>
+        <v>618</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>366</v>
-      </c>
-      <c r="G18" s="4"/>
+        <v>361</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>12</v>
+        <v>977</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>612</v>
+        <v>977</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="G21" s="4"/>
+        <v>260</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>976</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8696,450 +8999,486 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>118</v>
+        <v>973</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>721</v>
-      </c>
-      <c r="G2" s="4"/>
+        <v>715</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>690</v>
+        <v>684</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>689</v>
-      </c>
-      <c r="G3" s="7"/>
+        <v>683</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>679</v>
-      </c>
-      <c r="G4" s="7"/>
+        <v>673</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>674</v>
-      </c>
-      <c r="G5" s="4"/>
+        <v>668</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>669</v>
-      </c>
-      <c r="G6" s="7"/>
+        <v>663</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>12</v>
+        <v>974</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>660</v>
-      </c>
-      <c r="G8" s="7"/>
+        <v>654</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>655</v>
-      </c>
-      <c r="G9" s="4"/>
+        <v>649</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="G10" s="1"/>
+        <v>644</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>716</v>
-      </c>
-      <c r="G11" s="7"/>
+        <v>710</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G12" s="4"/>
+      <c r="G12" s="4" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>708</v>
-      </c>
-      <c r="G13" s="7"/>
+        <v>702</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>704</v>
-      </c>
-      <c r="G14" s="4"/>
+        <v>698</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="C15" s="8" t="s">
+        <v>690</v>
+      </c>
+      <c r="D15" s="8" t="s">
         <v>696</v>
       </c>
-      <c r="D15" s="8" t="s">
-        <v>702</v>
-      </c>
       <c r="E15" s="8" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>12</v>
+        <v>975</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="C16" s="5" t="s">
+        <v>690</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>696</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>702</v>
-      </c>
       <c r="E16" s="5" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>700</v>
-      </c>
-      <c r="G16" s="4"/>
+        <v>694</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>696</v>
-      </c>
-      <c r="G17" s="7"/>
+        <v>690</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>684</v>
-      </c>
-      <c r="G18" s="4"/>
+        <v>678</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>684</v>
-      </c>
-      <c r="G19" s="7"/>
+        <v>678</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>694</v>
-      </c>
-      <c r="G20" s="4"/>
+        <v>688</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>684</v>
-      </c>
-      <c r="G21" s="4"/>
+        <v>678</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>975</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
